--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_coquimbo.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:24</t>
+    <t xml:space="preserve">2026-09-24 01:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -730,19 +730,19 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="11">
@@ -753,19 +753,19 @@
         <v>19</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="12">
@@ -776,19 +776,19 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="13">
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.56</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="14">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_coquimbo.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:15</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2021_coquimbo.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
